--- a/backend-fastapi/app/static/templates/supplier_boarding_form.xlsx
+++ b/backend-fastapi/app/static/templates/supplier_boarding_form.xlsx
@@ -125,7 +125,7 @@
     <t>This part must be filled by Supplier directly and forwarded on excel format to the buyer</t>
   </si>
   <si>
-    <t>for V.Ships use only - this part must be filled by the buyer requesting the supplier addition</t>
+    <t>for HMZC use only - this part must be filled by the buyer requesting the supplier addition</t>
   </si>
   <si>
     <t xml:space="preserve">RFQ Number reference (if any) </t>
@@ -152,7 +152,7 @@
     <t>Client Mandated Request? (Y/N)</t>
   </si>
   <si>
-    <t>for V.Ships use only - this part must be filled by the buyer requesting the supplier re-activtion</t>
+    <t>for HMZC use only - this part must be filled by the buyer requesting the supplier re-activtion</t>
   </si>
   <si>
     <t>Date required until (de-activation date)</t>
@@ -2650,9 +2650,7 @@
       <c r="A5" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="179" t="s">
-        <v>236</v>
-      </c>
+      <c r="B5" s="179"/>
       <c r="C5" s="179"/>
       <c r="D5" s="179"/>
       <c r="E5" s="179"/>
@@ -2663,9 +2661,7 @@
         <v>41</v>
       </c>
       <c r="J5" s="163"/>
-      <c r="K5" s="126" t="s">
-        <v>254</v>
-      </c>
+      <c r="K5" s="126"/>
       <c r="L5" s="127"/>
       <c r="M5" s="128"/>
       <c r="N5" s="1"/>
@@ -2711,16 +2707,12 @@
       <c r="A7" s="178" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="192" t="s">
-        <v>237</v>
-      </c>
+      <c r="B7" s="192"/>
       <c r="C7" s="103"/>
       <c r="D7" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="132" t="s">
-        <v>240</v>
-      </c>
+      <c r="E7" s="132"/>
       <c r="F7" s="132"/>
       <c r="G7" s="17"/>
       <c r="H7" s="23"/>
@@ -2834,9 +2826,7 @@
       <c r="B11" s="193"/>
       <c r="C11" s="169"/>
       <c r="D11" s="169"/>
-      <c r="E11" s="132" t="s">
-        <v>238</v>
-      </c>
+      <c r="E11" s="132"/>
       <c r="F11" s="132"/>
       <c r="G11" s="18"/>
       <c r="H11" s="24"/>
@@ -2954,9 +2944,7 @@
         <v>235</v>
       </c>
       <c r="D15" s="195"/>
-      <c r="E15" s="132" t="s">
-        <v>147</v>
-      </c>
+      <c r="E15" s="132"/>
       <c r="F15" s="132"/>
       <c r="G15" s="71"/>
       <c r="H15" s="72"/>
@@ -3071,16 +3059,12 @@
       <c r="A19" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="106" t="s">
-        <v>242</v>
-      </c>
+      <c r="B19" s="106"/>
       <c r="C19" s="103"/>
       <c r="D19" s="169" t="s">
         <v>1</v>
       </c>
-      <c r="E19" s="196" t="s">
-        <v>244</v>
-      </c>
+      <c r="E19" s="196"/>
       <c r="F19" s="196"/>
       <c r="G19" s="62"/>
       <c r="H19" s="75"/>
@@ -3136,9 +3120,7 @@
       <c r="A21" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="106" t="s">
-        <v>242</v>
-      </c>
+      <c r="B21" s="106"/>
       <c r="C21" s="102"/>
       <c r="D21" s="169"/>
       <c r="E21" s="196"/>
@@ -3151,9 +3133,7 @@
       </c>
       <c r="K21" s="115"/>
       <c r="L21" s="202"/>
-      <c r="M21" s="111">
-        <v>10</v>
-      </c>
+      <c r="M21" s="111"/>
       <c r="N21" s="3"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="49"/>
@@ -3196,16 +3176,12 @@
       <c r="A23" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="107">
-        <v>42</v>
-      </c>
+      <c r="B23" s="107"/>
       <c r="C23" s="14"/>
       <c r="D23" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="E23" s="132" t="s">
-        <v>245</v>
-      </c>
+      <c r="E23" s="132"/>
       <c r="F23" s="132"/>
       <c r="G23" s="17"/>
       <c r="H23" s="23"/>
@@ -3264,16 +3240,12 @@
       <c r="A25" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="106" t="s">
-        <v>243</v>
-      </c>
+      <c r="B25" s="106"/>
       <c r="C25" s="31"/>
       <c r="D25" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="132" t="s">
-        <v>245</v>
-      </c>
+      <c r="E25" s="132"/>
       <c r="F25" s="132"/>
       <c r="G25" s="18"/>
       <c r="H25" s="24"/>
@@ -3371,15 +3343,11 @@
       <c r="A28" s="137" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="138">
-        <v>5001114387</v>
-      </c>
+      <c r="B28" s="138"/>
       <c r="C28" s="103"/>
       <c r="D28" s="25"/>
       <c r="E28" s="25"/>
-      <c r="F28" s="11" t="s">
-        <v>96</v>
-      </c>
+      <c r="F28" s="11"/>
       <c r="G28" s="17"/>
       <c r="H28" s="23"/>
       <c r="I28" s="20"/>
@@ -3751,9 +3719,7 @@
       <c r="A40" s="53" t="s">
         <v>73</v>
       </c>
-      <c r="B40" s="108" t="s">
-        <v>246</v>
-      </c>
+      <c r="B40" s="108"/>
       <c r="C40" s="14"/>
       <c r="D40" s="53" t="s">
         <v>100</v>
@@ -3825,9 +3791,7 @@
       <c r="A42" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B42" s="108" t="s">
-        <v>247</v>
-      </c>
+      <c r="B42" s="108"/>
       <c r="C42" s="14"/>
       <c r="D42" s="53" t="s">
         <v>76</v>
@@ -3893,9 +3857,7 @@
       <c r="A44" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="108" t="s">
-        <v>248</v>
-      </c>
+      <c r="B44" s="108"/>
       <c r="C44" s="14"/>
       <c r="D44" s="53" t="s">
         <v>77</v>
@@ -3959,9 +3921,7 @@
       <c r="A46" s="53" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="108" t="s">
-        <v>249</v>
-      </c>
+      <c r="B46" s="108"/>
       <c r="C46" s="14"/>
       <c r="D46" s="53" t="s">
         <v>78</v>
@@ -4089,9 +4049,7 @@
       <c r="A50" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="108" t="s">
-        <v>250</v>
-      </c>
+      <c r="B50" s="108"/>
       <c r="C50" s="14"/>
       <c r="D50" s="53" t="s">
         <v>80</v>
@@ -4155,9 +4113,7 @@
       <c r="A52" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="B52" s="114" t="s">
-        <v>251</v>
-      </c>
+      <c r="B52" s="114"/>
       <c r="C52" s="14"/>
       <c r="D52" s="92"/>
       <c r="E52" s="92"/>
@@ -4341,17 +4297,13 @@
       <c r="A58" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B58" s="142" t="s">
-        <v>252</v>
-      </c>
+      <c r="B58" s="142"/>
       <c r="C58" s="143"/>
       <c r="D58" s="25" t="s">
         <v>19</v>
       </c>
       <c r="E58" s="25"/>
-      <c r="F58" s="106" t="s">
-        <v>257</v>
-      </c>
+      <c r="F58" s="106"/>
       <c r="G58" s="17"/>
       <c r="H58" s="16"/>
       <c r="I58" s="70"/>
@@ -4411,9 +4363,7 @@
       <c r="A60" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B60" s="145" t="s">
-        <v>255</v>
-      </c>
+      <c r="B60" s="145"/>
       <c r="C60" s="103"/>
       <c r="D60" s="103"/>
       <c r="E60" s="103"/>
@@ -4477,9 +4427,7 @@
         <v>20</v>
       </c>
       <c r="E62" s="25"/>
-      <c r="F62" s="106">
-        <v>63216107474</v>
-      </c>
+      <c r="F62" s="106"/>
       <c r="G62" s="17"/>
       <c r="H62" s="16"/>
       <c r="I62" s="70"/>
@@ -4535,17 +4483,13 @@
       <c r="A64" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B64" s="106" t="s">
-        <v>253</v>
-      </c>
+      <c r="B64" s="106"/>
       <c r="C64" s="103"/>
       <c r="D64" s="25" t="s">
         <v>21</v>
       </c>
       <c r="E64" s="25"/>
-      <c r="F64" s="106">
-        <v>251650</v>
-      </c>
+      <c r="F64" s="106"/>
       <c r="G64" s="17"/>
       <c r="H64" s="16"/>
       <c r="I64" s="70"/>
@@ -4609,9 +4553,7 @@
         <v>22</v>
       </c>
       <c r="E66" s="25"/>
-      <c r="F66" s="106" t="s">
-        <v>258</v>
-      </c>
+      <c r="F66" s="106"/>
       <c r="G66" s="17"/>
       <c r="H66" s="16"/>
       <c r="I66" s="70"/>
@@ -4667,9 +4609,7 @@
       <c r="A68" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B68" s="106" t="s">
-        <v>256</v>
-      </c>
+      <c r="B68" s="106"/>
       <c r="C68" s="103"/>
       <c r="D68" s="25" t="s">
         <v>23</v>
